--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_211_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_211_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5901</v>
+        <v>2.8905</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8312</v>
+        <v>2.4341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7589</v>
+        <v>0.4564</v>
       </c>
       <c r="G2" t="n">
         <v>2.1143</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2464</v>
+        <v>-0.4531</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4753</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7218</v>
+        <v>0.4193</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3943</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2202</v>
+        <v>2.8182</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9953</v>
+        <v>2.1398</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2249</v>
+        <v>0.6784</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6484</v>
+        <v>3.0886</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6818</v>
+        <v>0.539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0334</v>
+        <v>2.5496</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9558</v>
+        <v>3.6532</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8822</v>
+        <v>0.6253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0736</v>
+        <v>3.0279</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3074</v>
+        <v>-0.5646</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2004</v>
+        <v>-0.0862</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.107</v>
+        <v>-0.4783</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5718</v>
+        <v>-0.0384</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4312</v>
+        <v>-0.3536</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1406</v>
+        <v>0.3152</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7429</v>
+        <v>2.3855</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8292</v>
+        <v>1.3623</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9137</v>
+        <v>1.0232</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0886</v>
+        <v>1.6484</v>
       </c>
       <c r="H4" t="n">
-        <v>0.539</v>
+        <v>1.6818</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5496</v>
+        <v>-0.0334</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6532</v>
+        <v>1.9558</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6253</v>
+        <v>1.8822</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0279</v>
+        <v>0.0736</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5646</v>
+        <v>-0.3074</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0862</v>
+        <v>-0.2004</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4783</v>
+        <v>-0.107</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1138</v>
+        <v>0.7371</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6642</v>
+        <v>0.7982</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5505</v>
+        <v>-0.0611</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5838</v>
+        <v>2.3547</v>
       </c>
       <c r="E5" t="n">
-        <v>2.036</v>
+        <v>1.6389</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5478</v>
+        <v>0.7158</v>
       </c>
       <c r="G5" t="n">
         <v>2.0563</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.3253</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1098</v>
+        <v>-0.507</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0136</v>
+        <v>0.1817</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5361</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4648</v>
+        <v>-0.4293</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0374</v>
+        <v>-0.4874</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4274</v>
+        <v>0.0581</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0241</v>
+        <v>-0.611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6659</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.104</v>
+        <v>-0.3813</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0672</v>
+        <v>-0.7359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0.3546</v>
       </c>
       <c r="M6" t="n">
-        <v>0.586</v>
+        <v>-0.1394</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0431</v>
+        <v>0.1249</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6291</v>
+        <v>-0.2643</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.1406</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1415</v>
+        <v>-0.1061</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0589</v>
+        <v>-0.0345</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.79</v>
+        <v>-0.4648</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.68</v>
+        <v>-0.0374</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1099</v>
+        <v>-0.4274</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.611</v>
+        <v>0.0241</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.6659</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3813</v>
+        <v>0.104</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7359</v>
+        <v>0.0672</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3546</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1394</v>
+        <v>0.586</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1249</v>
+        <v>-0.0431</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2643</v>
+        <v>0.6291</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5012</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-0.1415</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2025</v>
+        <v>0.0589</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0545</v>
+        <v>-1.189</v>
       </c>
       <c r="E8" t="n">
         <v>0.0442</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0988</v>
+        <v>-1.2332</v>
       </c>
       <c r="G8" t="n">
         <v>0.5583</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1643</v>
+        <v>-0.2987</v>
       </c>
       <c r="T8" t="n">
         <v>-0.8215</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6572</v>
+        <v>0.5228</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1444</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3588</v>
+        <v>-2.2899</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5569</v>
+        <v>-2.9767</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1981</v>
+        <v>0.6867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4241</v>
+        <v>-1.8713</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1849</v>
+        <v>-0.4192</v>
       </c>
       <c r="I9" t="n">
-        <v>0.609</v>
+        <v>-1.4521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1169</v>
+        <v>-0.9207</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.077</v>
+        <v>-0.208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1939</v>
+        <v>-0.7127</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3072</v>
+        <v>-0.9505</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1078</v>
+        <v>-0.2112</v>
       </c>
       <c r="O9" t="n">
-        <v>0.415</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.871</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2315</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0553</v>
+        <v>-0.8962</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2869</v>
+        <v>0.0136</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4318</v>
+        <v>-2.3013</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0513</v>
+        <v>-4.6002</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6195000000000001</v>
+        <v>2.2989</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8713</v>
+        <v>0.4241</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4192</v>
+        <v>-0.1849</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4521</v>
+        <v>0.609</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9207</v>
+        <v>0.1169</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.208</v>
+        <v>-0.077</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7127</v>
+        <v>0.1939</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9505</v>
+        <v>0.3072</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2112</v>
+        <v>-0.1078</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-4.871</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0244</v>
+        <v>-0.174</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>0.0121</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0536</v>
+        <v>-0.186</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7365</v>
+        <v>-2.736</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2056</v>
+        <v>-2.5411</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5309</v>
+        <v>-0.1949</v>
       </c>
       <c r="G11" t="n">
         <v>-1.809</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3012</v>
+        <v>-0.3007</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.955</v>
+        <v>-0.2906</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3462</v>
+        <v>-0.0101</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.785</v>
+        <v>-4.3051</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2613</v>
+        <v>-3.4789</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.8262</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0933</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3</v>
+        <v>0.1799</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.963</v>
+        <v>-0.1806</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6629</v>
+        <v>0.3605</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.571</v>
+        <v>-8.042299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.254</v>
+        <v>-5.0614</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.317</v>
+        <v>-2.9809</v>
       </c>
       <c r="G13" t="n">
         <v>-2.819</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2829</v>
+        <v>0.2458</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1221</v>
+        <v>0.3148</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.405</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.5413</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.0554</v>
+        <v>-11.3088</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.3106</v>
+        <v>-11.5638</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2552000000000003</v>
+        <v>0.2549000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4667000000000003</v>
+        <v>0.4666999999999986</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.357100000000001</v>
+        <v>-1.3571</v>
       </c>
       <c r="I14" t="n">
         <v>1.824000000000001</v>
@@ -1522,7 +1522,7 @@
         <v>6.417899999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3457999999999994</v>
+        <v>0.3458000000000008</v>
       </c>
       <c r="L14" t="n">
         <v>6.0722</v>
@@ -1546,10 +1546,10 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2799</v>
+        <v>-1.5332</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7913</v>
+        <v>-3.044500000000001</v>
       </c>
       <c r="U14" t="n">
         <v>1.5113</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.1185</v>
+        <v>10.4344</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0166</v>
+        <v>6.4884</v>
       </c>
       <c r="F15" t="n">
-        <v>4.102</v>
+        <v>3.946</v>
       </c>
       <c r="G15" t="n">
         <v>4.4697</v>
@@ -1624,13 +1624,13 @@
         <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1617</v>
+        <v>0.4775</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6642</v>
+        <v>-0.1924</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8259</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>3.8634</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3317</v>
+        <v>6.0901</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6607</v>
+        <v>3.071</v>
       </c>
       <c r="F16" t="n">
-        <v>2.671</v>
+        <v>3.0191</v>
       </c>
       <c r="G16" t="n">
         <v>0.9304</v>
@@ -1702,13 +1702,13 @@
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7929</v>
+        <v>0.5513</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6765</v>
+        <v>0.0868</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1164</v>
+        <v>0.4646</v>
       </c>
       <c r="V16" t="n">
         <v>3.2166</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4377</v>
+        <v>1.6793</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1494</v>
+        <v>-0.0315</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5871</v>
+        <v>1.7108</v>
       </c>
       <c r="G17" t="n">
         <v>0.5452</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1797</v>
+        <v>0.0619</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8215</v>
+        <v>-0.7035</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6418</v>
+        <v>0.7655</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2178</v>
+        <v>0.4308</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9728</v>
+        <v>-0.2067</v>
       </c>
       <c r="F18" t="n">
-        <v>0.245</v>
+        <v>0.6375</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3136</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2814</v>
+        <v>0.4944</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6201</v>
+        <v>0.4406</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3387</v>
+        <v>0.0538</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6778999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.197</v>
+        <v>0.0445</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2222</v>
+        <v>0.5934</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0252</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2977</v>
+        <v>1.7055</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3313</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6291</v>
+        <v>0.8532</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2654</v>
+        <v>3.1103</v>
       </c>
       <c r="K19" t="n">
-        <v>0.521</v>
+        <v>1.1497</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7863</v>
+        <v>1.9606</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0323</v>
+        <v>-1.4048</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>-0.2974</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>-1.1074</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6365</v>
+        <v>-0.0373</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4876</v>
+        <v>-0.1098</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1489</v>
+        <v>0.0725</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4821</v>
+        <v>-0.1004</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6129</v>
+        <v>-0.1316</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1308</v>
+        <v>0.0312</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2095</v>
+        <v>-0.2977</v>
       </c>
       <c r="H20" t="n">
-        <v>0.461</v>
+        <v>0.3313</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.6706</v>
+        <v>-0.6291</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8586</v>
+        <v>-0.2654</v>
       </c>
       <c r="K20" t="n">
-        <v>0.39</v>
+        <v>0.521</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.2486</v>
+        <v>-0.7863</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3509</v>
+        <v>-0.0323</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.1896</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.422</v>
+        <v>0.1573</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4929</v>
+        <v>0.3391</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7389</v>
+        <v>0.1338</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2318</v>
+        <v>0.2054</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0026</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-0.1418</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5833</v>
+        <v>-0.3971</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5934</v>
+        <v>-1.259</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1767</v>
+        <v>0.8619</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7055</v>
+        <v>-3.2095</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.461</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8532</v>
+        <v>-3.6706</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1103</v>
+        <v>-1.8586</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1497</v>
+        <v>0.39</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9606</v>
+        <v>-2.2486</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4048</v>
+        <v>-1.3509</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2974</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1074</v>
+        <v>-1.422</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6651</v>
+        <v>0.5779</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1098</v>
+        <v>-0.3851</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5553</v>
+        <v>0.963</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.0026</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7726</v>
+        <v>-0.6239</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.395</v>
+        <v>-2.4218</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6224</v>
+        <v>1.7979</v>
       </c>
       <c r="G22" t="n">
-        <v>0.603</v>
+        <v>-2.4113</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7635</v>
+        <v>0.5533</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1605</v>
+        <v>-2.9646</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5966</v>
+        <v>-1.5106</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8605</v>
+        <v>0.3466</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7361</v>
+        <v>-1.8572</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9937</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.097</v>
+        <v>0.2067</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8966</v>
+        <v>-1.1074</v>
       </c>
       <c r="P22" t="n">
         <v>-0.4639</v>
@@ -2170,28 +2170,28 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3756</v>
+        <v>0.5012</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6721</v>
+        <v>-0.3418</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2965</v>
+        <v>0.843</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>1.7501</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4546</v>
+        <v>-0.7047</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8937</v>
+        <v>-1.1591</v>
       </c>
       <c r="F23" t="n">
-        <v>1.439</v>
+        <v>0.4543</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4113</v>
+        <v>0.603</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5533</v>
+        <v>0.7635</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9646</v>
+        <v>-0.1605</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5106</v>
+        <v>1.5966</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3466</v>
+        <v>0.8605</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8572</v>
+        <v>0.7361</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.9937</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2067</v>
+        <v>-0.097</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1074</v>
+        <v>-0.8966</v>
       </c>
       <c r="P23" t="n">
         <v>-0.4639</v>
@@ -2248,22 +2248,22 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3295</v>
+        <v>-0.3077</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8136</v>
+        <v>-0.4362</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4841</v>
+        <v>0.1285</v>
       </c>
       <c r="V23" t="n">
-        <v>1.7501</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4696</v>
+        <v>-0.779</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2476</v>
+        <v>-1.6578</v>
       </c>
       <c r="F24" t="n">
-        <v>0.778</v>
+        <v>0.8788</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6916</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3141</v>
+        <v>0.3765</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4327</v>
+        <v>0.5335</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.485</v>
+        <v>-2.4457</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3501</v>
+        <v>-2.4681</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1349</v>
+        <v>0.0224</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7969</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7784</v>
+        <v>0.8178</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2715</v>
+        <v>0.1535</v>
       </c>
       <c r="U25" t="n">
-        <v>0.507</v>
+        <v>0.6642</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4665</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.0555</v>
+        <v>13.6283</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8170000000000011</v>
+        <v>0.8171999999999993</v>
       </c>
       <c r="F26" t="n">
-        <v>11.2385</v>
+        <v>12.811</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4668000000000003</v>
+        <v>-0.4668000000000008</v>
       </c>
       <c r="H26" t="n">
         <v>1.357</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.824</v>
+        <v>-1.823999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>5.951</v>
@@ -2461,10 +2461,10 @@
         <v>1.7027</v>
       </c>
       <c r="L26" t="n">
-        <v>4.2483</v>
+        <v>4.248299999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.4177</v>
+        <v>-6.417700000000001</v>
       </c>
       <c r="N26" t="n">
         <v>-0.3455999999999999</v>
@@ -2473,7 +2473,7 @@
         <v>-6.0722</v>
       </c>
       <c r="P26" t="n">
-        <v>1.159799999999999</v>
+        <v>1.1598</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.2369</v>
@@ -2482,13 +2482,13 @@
         <v>17.3965</v>
       </c>
       <c r="S26" t="n">
-        <v>2.279800000000001</v>
+        <v>3.8526</v>
       </c>
       <c r="T26" t="n">
         <v>-1.5112</v>
       </c>
       <c r="U26" t="n">
-        <v>3.7911</v>
+        <v>5.3639</v>
       </c>
       <c r="V26" t="n">
         <v>9.082600000000001</v>
